--- a/Excel_practice.xlsx
+++ b/Excel_practice.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analytics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASDC24\Desktop\Vinayak\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F4C73D-A0B5-4CAF-AFA6-F4BD1D81DC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78AE916A-F15F-4B79-ACF0-787A72C1DE0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="9" xr2:uid="{7B226811-10E8-442B-93CE-D6B46625704C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="19" activeTab="21" xr2:uid="{7B226811-10E8-442B-93CE-D6B46625704C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,18 +23,41 @@
     <sheet name="Sheet8" sheetId="9" r:id="rId8"/>
     <sheet name="Sheet9" sheetId="10" r:id="rId9"/>
     <sheet name="Sheet10" sheetId="11" r:id="rId10"/>
+    <sheet name="Sheet11" sheetId="12" r:id="rId11"/>
+    <sheet name="Sheet12" sheetId="13" r:id="rId12"/>
+    <sheet name="Sheet13" sheetId="14" r:id="rId13"/>
+    <sheet name="Sheet14" sheetId="15" r:id="rId14"/>
+    <sheet name="Sheet15" sheetId="16" r:id="rId15"/>
+    <sheet name="Sheet23" sheetId="24" r:id="rId16"/>
+    <sheet name="Sheet16" sheetId="17" r:id="rId17"/>
+    <sheet name="Sheet17" sheetId="18" r:id="rId18"/>
+    <sheet name="Sheet18" sheetId="19" r:id="rId19"/>
+    <sheet name="Sheet19" sheetId="20" r:id="rId20"/>
+    <sheet name="Sheet20" sheetId="21" r:id="rId21"/>
+    <sheet name="Sheet21" sheetId="22" r:id="rId22"/>
+    <sheet name="Sheet22" sheetId="23" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="239">
   <si>
     <t>Employee ID</t>
   </si>
@@ -515,6 +538,255 @@
   <si>
     <t xml:space="preserve">Employee Name </t>
   </si>
+  <si>
+    <t>Raw Email</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>arjun.patel92@gmail.com</t>
+  </si>
+  <si>
+    <t>neha.verma.design@outlook.com</t>
+  </si>
+  <si>
+    <t>techguru_rahul@yahoo.com</t>
+  </si>
+  <si>
+    <t>priya.kapoor@protonmail.com</t>
+  </si>
+  <si>
+    <t>devansh.mehta@icloud.com</t>
+  </si>
+  <si>
+    <t>curiousmind123@zoho.com</t>
+  </si>
+  <si>
+    <t>ankit.shah.dev@mail.com</t>
+  </si>
+  <si>
+    <t>simran.kaur88@aol.com</t>
+  </si>
+  <si>
+    <t>rohan.das@fastmail.com</t>
+  </si>
+  <si>
+    <t>learning.with.ria@gmx.com</t>
+  </si>
+  <si>
+    <t>yash_trivedi@rediffmail.com</t>
+  </si>
+  <si>
+    <t>coder.vikas@tutanota.com</t>
+  </si>
+  <si>
+    <t>sneha.joshi@live.com</t>
+  </si>
+  <si>
+    <t>rajdeep.singh@inbox.com</t>
+  </si>
+  <si>
+    <t>digital.nomad.adi@hey.com</t>
+  </si>
+  <si>
+    <t>kavya.nair@hushmail.com</t>
+  </si>
+  <si>
+    <t>amitabh_rocks@lycos.com</t>
+  </si>
+  <si>
+    <t>shreya.banerjee@web.de</t>
+  </si>
+  <si>
+    <t>future.ceo.manav@posteo.net</t>
+  </si>
+  <si>
+    <t>nisha.creates@runbox.com</t>
+  </si>
+  <si>
+    <t>Faculty Name</t>
+  </si>
+  <si>
+    <t>Class Conducted</t>
+  </si>
+  <si>
+    <t>Attendance %</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>Rajesh</t>
+  </si>
+  <si>
+    <t>Sunita</t>
+  </si>
+  <si>
+    <t>Manoj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavita </t>
+  </si>
+  <si>
+    <t>Anil</t>
+  </si>
+  <si>
+    <t>Rajveer</t>
+  </si>
+  <si>
+    <t>Perfomance using logical operators</t>
+  </si>
+  <si>
+    <t>Logical formulas</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Salary Bonus Check</t>
+  </si>
+  <si>
+    <t>Bonus Status</t>
+  </si>
+  <si>
+    <t>Aarav Sharma</t>
+  </si>
+  <si>
+    <t>Kavya Iyer</t>
+  </si>
+  <si>
+    <t>Rohan Mehta</t>
+  </si>
+  <si>
+    <t>Sneha Patel</t>
+  </si>
+  <si>
+    <t>Arjun Reddy</t>
+  </si>
+  <si>
+    <t>Neha Gupta</t>
+  </si>
+  <si>
+    <t>Vikram Singh</t>
+  </si>
+  <si>
+    <t>Priya Nair</t>
+  </si>
+  <si>
+    <t>Rahul Verma</t>
+  </si>
+  <si>
+    <t>Ananya Das</t>
+  </si>
+  <si>
+    <t>Karan Malhotra</t>
+  </si>
+  <si>
+    <t>Pooja Chatterjee</t>
+  </si>
+  <si>
+    <t>Aditya Joshi</t>
+  </si>
+  <si>
+    <t>Meera Kulkarni</t>
+  </si>
+  <si>
+    <t>Siddharth Jain</t>
+  </si>
+  <si>
+    <t>Isha Kapoor</t>
+  </si>
+  <si>
+    <t>Dev Patel</t>
+  </si>
+  <si>
+    <t>Tanvi Desai</t>
+  </si>
+  <si>
+    <t>Manish Tiwari</t>
+  </si>
+  <si>
+    <t>Riya Sen</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>Nestede IF</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Experience(Years)</t>
+  </si>
+  <si>
+    <t>Eligible</t>
+  </si>
+  <si>
+    <t>Assignment Submitted</t>
+  </si>
+  <si>
+    <t>Exam Eligibility</t>
+  </si>
+  <si>
+    <t>Customer Name</t>
+  </si>
+  <si>
+    <t>Purchase Amount</t>
+  </si>
+  <si>
+    <t>Membership</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No Discount</t>
+  </si>
+  <si>
+    <t>Applicant</t>
+  </si>
+  <si>
+    <t>CIBIL Score</t>
+  </si>
+  <si>
+    <t>Loan Status</t>
+  </si>
+  <si>
+    <t>Present</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Absent</t>
+  </si>
+  <si>
+    <t>Number 1</t>
+  </si>
+  <si>
+    <t>Number 2</t>
+  </si>
+  <si>
+    <t>targets Achieved</t>
+  </si>
+  <si>
+    <t>Data Set Combined logic</t>
+  </si>
 </sst>
 </file>
 
@@ -524,7 +796,7 @@
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -610,8 +882,16 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -636,8 +916,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -682,11 +968,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -748,6 +1058,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -773,6 +1092,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1145,16 +1479,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B11CE51-44F3-4CF4-8D9F-7C13C1E178D2}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1171,7 +1505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -1188,7 +1522,7 @@
         <v>45298</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
@@ -1205,7 +1539,7 @@
         <v>40398</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
@@ -1222,7 +1556,7 @@
         <v>43810</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>13</v>
       </c>
@@ -1239,7 +1573,7 @@
         <v>43034</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
@@ -1256,7 +1590,7 @@
         <v>44044</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
@@ -1273,7 +1607,7 @@
         <v>42767</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>18</v>
       </c>
@@ -1290,7 +1624,7 @@
         <v>43297</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>19</v>
       </c>
@@ -1307,7 +1641,7 @@
         <v>43809</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>20</v>
       </c>
@@ -1324,7 +1658,7 @@
         <v>42211</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>21</v>
       </c>
@@ -1341,7 +1675,7 @@
         <v>43575</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="19.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>22</v>
       </c>
@@ -1359,7 +1693,7 @@
       </c>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:6" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>23</v>
       </c>
@@ -1376,7 +1710,7 @@
         <v>46080</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>24</v>
       </c>
@@ -1393,7 +1727,7 @@
         <v>45283</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>25</v>
       </c>
@@ -1410,7 +1744,7 @@
         <v>43824</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>26</v>
       </c>
@@ -1427,7 +1761,7 @@
         <v>45192</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>27</v>
       </c>
@@ -1444,7 +1778,7 @@
         <v>43384</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>28</v>
       </c>
@@ -1461,7 +1795,7 @@
         <v>40517</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>29</v>
       </c>
@@ -1478,7 +1812,7 @@
         <v>44366</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>30</v>
       </c>
@@ -1495,7 +1829,7 @@
         <v>41253</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>31</v>
       </c>
@@ -1522,13 +1856,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3785BD7D-C258-4097-A1DC-2883E2E1E3E4}">
   <dimension ref="A2:B22"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.88671875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.88671875" style="10"/>
+    <col min="1" max="1" width="16.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.85546875" style="10"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>155</v>
       </c>
@@ -1536,7 +1870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>6</v>
       </c>
@@ -1544,7 +1878,7 @@
         <v>37790</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>9</v>
       </c>
@@ -1552,7 +1886,7 @@
         <v>81534</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
         <v>12</v>
       </c>
@@ -1560,7 +1894,7 @@
         <v>80663</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>14</v>
       </c>
@@ -1568,7 +1902,7 @@
         <v>35032</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>16</v>
       </c>
@@ -1576,7 +1910,7 @@
         <v>29155</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
         <v>32</v>
       </c>
@@ -1584,7 +1918,7 @@
         <v>38748</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>33</v>
       </c>
@@ -1592,7 +1926,7 @@
         <v>34012</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>34</v>
       </c>
@@ -1600,7 +1934,7 @@
         <v>39943</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>35</v>
       </c>
@@ -1608,7 +1942,7 @@
         <v>42597</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
         <v>36</v>
       </c>
@@ -1616,7 +1950,7 @@
         <v>90620</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>37</v>
       </c>
@@ -1624,7 +1958,7 @@
         <v>89733</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
         <v>38</v>
       </c>
@@ -1632,7 +1966,7 @@
         <v>60242</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>39</v>
       </c>
@@ -1640,7 +1974,7 @@
         <v>42035</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
         <v>40</v>
       </c>
@@ -1648,7 +1982,7 @@
         <v>71838</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
         <v>41</v>
       </c>
@@ -1656,7 +1990,7 @@
         <v>92265</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
         <v>42</v>
       </c>
@@ -1664,7 +1998,7 @@
         <v>80312</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
         <v>43</v>
       </c>
@@ -1672,7 +2006,7 @@
         <v>34557</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
         <v>44</v>
       </c>
@@ -1680,7 +2014,7 @@
         <v>21193</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>45</v>
       </c>
@@ -1688,7 +2022,7 @@
         <v>29120</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
         <v>46</v>
       </c>
@@ -1715,23 +2049,2711 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2392B7DF-0EEB-4FDD-B717-FEF14FF48D9D}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="30.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" s="10" t="str">
+        <f>TRIM(A2)</f>
+        <v>arjun.patel92@gmail.com</v>
+      </c>
+      <c r="C2" s="10" t="str">
+        <f>LEFT(B2,FIND("@",B2)-1)</f>
+        <v>arjun.patel92</v>
+      </c>
+      <c r="D2" s="10" t="str">
+        <f>RIGHT(B2,LEN(B2)-FIND("@",B2))</f>
+        <v>gmail.com</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="10" t="str">
+        <f t="shared" ref="B3:B21" si="0">TRIM(A3)</f>
+        <v>neha.verma.design@outlook.com</v>
+      </c>
+      <c r="C3" s="10" t="str">
+        <f t="shared" ref="C3:C21" si="1">LEFT(B3,FIND("@",B3)-1)</f>
+        <v>neha.verma.design</v>
+      </c>
+      <c r="D3" s="10" t="str">
+        <f t="shared" ref="D3:D21" si="2">RIGHT(B3,LEN(B3)-FIND("@",B3))</f>
+        <v>outlook.com</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>techguru_rahul@yahoo.com</v>
+      </c>
+      <c r="C4" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>techguru_rahul</v>
+      </c>
+      <c r="D4" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>yahoo.com</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>priya.kapoor@protonmail.com</v>
+      </c>
+      <c r="C5" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>priya.kapoor</v>
+      </c>
+      <c r="D5" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>protonmail.com</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>devansh.mehta@icloud.com</v>
+      </c>
+      <c r="C6" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>devansh.mehta</v>
+      </c>
+      <c r="D6" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>icloud.com</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>curiousmind123@zoho.com</v>
+      </c>
+      <c r="C7" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>curiousmind123</v>
+      </c>
+      <c r="D7" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>zoho.com</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>ankit.shah.dev@mail.com</v>
+      </c>
+      <c r="C8" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>ankit.shah.dev</v>
+      </c>
+      <c r="D8" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>mail.com</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>simran.kaur88@aol.com</v>
+      </c>
+      <c r="C9" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>simran.kaur88</v>
+      </c>
+      <c r="D9" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>aol.com</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>rohan.das@fastmail.com</v>
+      </c>
+      <c r="C10" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>rohan.das</v>
+      </c>
+      <c r="D10" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>fastmail.com</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>learning.with.ria@gmx.com</v>
+      </c>
+      <c r="C11" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>learning.with.ria</v>
+      </c>
+      <c r="D11" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>gmx.com</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>yash_trivedi@rediffmail.com</v>
+      </c>
+      <c r="C12" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>yash_trivedi</v>
+      </c>
+      <c r="D12" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>rediffmail.com</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B13" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>coder.vikas@tutanota.com</v>
+      </c>
+      <c r="C13" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>coder.vikas</v>
+      </c>
+      <c r="D13" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>tutanota.com</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B14" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>sneha.joshi@live.com</v>
+      </c>
+      <c r="C14" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>sneha.joshi</v>
+      </c>
+      <c r="D14" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>live.com</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B15" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>rajdeep.singh@inbox.com</v>
+      </c>
+      <c r="C15" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>rajdeep.singh</v>
+      </c>
+      <c r="D15" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>inbox.com</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B16" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>digital.nomad.adi@hey.com</v>
+      </c>
+      <c r="C16" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>digital.nomad.adi</v>
+      </c>
+      <c r="D16" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>hey.com</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B17" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>kavya.nair@hushmail.com</v>
+      </c>
+      <c r="C17" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>kavya.nair</v>
+      </c>
+      <c r="D17" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>hushmail.com</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B18" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>amitabh_rocks@lycos.com</v>
+      </c>
+      <c r="C18" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>amitabh_rocks</v>
+      </c>
+      <c r="D18" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>lycos.com</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B19" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>shreya.banerjee@web.de</v>
+      </c>
+      <c r="C19" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>shreya.banerjee</v>
+      </c>
+      <c r="D19" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>web.de</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>future.ceo.manav@posteo.net</v>
+      </c>
+      <c r="C20" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>future.ceo.manav</v>
+      </c>
+      <c r="D20" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>posteo.net</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B21" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>nisha.creates@runbox.com</v>
+      </c>
+      <c r="C21" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>nisha.creates</v>
+      </c>
+      <c r="D21" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>runbox.com</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA29F89-1D5D-4FE0-B4A1-6AB943433487}">
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="55" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" s="38">
+        <v>45</v>
+      </c>
+      <c r="C3" s="38">
+        <v>92</v>
+      </c>
+      <c r="D3" s="38" t="str">
+        <f>IF(AND(C3&gt;=90,B3&gt;=40),"Excellent",IF(C3&gt;40,"Good","Needs Improvement"))</f>
+        <v>Excellent</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="38">
+        <v>38</v>
+      </c>
+      <c r="C4" s="38">
+        <v>85</v>
+      </c>
+      <c r="D4" s="38" t="str">
+        <f t="shared" ref="D4:D7" si="0">IF(AND(C4&gt;=90,B4&gt;=40),"Excellent",IF(C4&gt;40,"Good","Needs Improvement"))</f>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="38">
+        <v>50</v>
+      </c>
+      <c r="C5" s="38">
+        <v>95</v>
+      </c>
+      <c r="D5" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Excellent</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="38">
+        <v>30</v>
+      </c>
+      <c r="C6" s="38">
+        <v>70</v>
+      </c>
+      <c r="D6" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="38">
+        <v>42</v>
+      </c>
+      <c r="C7" s="38">
+        <v>88</v>
+      </c>
+      <c r="D7" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="B8" s="41">
+        <v>32</v>
+      </c>
+      <c r="C8" s="41">
+        <v>38</v>
+      </c>
+      <c r="D8" s="38" t="str">
+        <f>IF(AND(C8&gt;=90,B8&gt;=40),"Excellent",IF(C8&gt;40,"Good","Needs Improvement"))</f>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" s="38">
+        <v>40</v>
+      </c>
+      <c r="C9" s="38">
+        <v>51</v>
+      </c>
+      <c r="D9" s="38" t="str">
+        <f t="shared" ref="D9:D23" si="1">IF(AND(C9&gt;=90,B9&gt;=40),"Excellent",IF(C9&gt;40,"Good","Needs Improvement"))</f>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="38">
+        <v>49</v>
+      </c>
+      <c r="C10" s="38">
+        <v>22</v>
+      </c>
+      <c r="D10" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="38">
+        <v>53</v>
+      </c>
+      <c r="C11" s="38">
+        <v>27</v>
+      </c>
+      <c r="D11" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12" s="38">
+        <v>43</v>
+      </c>
+      <c r="C12" s="38">
+        <v>24</v>
+      </c>
+      <c r="D12" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="B13" s="38">
+        <v>39</v>
+      </c>
+      <c r="C13" s="38">
+        <v>11</v>
+      </c>
+      <c r="D13" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="B14" s="38">
+        <v>42</v>
+      </c>
+      <c r="C14" s="38">
+        <v>24</v>
+      </c>
+      <c r="D14" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="B15" s="38">
+        <v>36</v>
+      </c>
+      <c r="C15" s="38">
+        <v>38</v>
+      </c>
+      <c r="D15" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="B16" s="38">
+        <v>41</v>
+      </c>
+      <c r="C16" s="38">
+        <v>31</v>
+      </c>
+      <c r="D16" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="B17" s="38">
+        <v>56</v>
+      </c>
+      <c r="C17" s="38">
+        <v>77</v>
+      </c>
+      <c r="D17" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="38">
+        <v>54</v>
+      </c>
+      <c r="C18" s="38">
+        <v>41</v>
+      </c>
+      <c r="D18" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="B19" s="38">
+        <v>45</v>
+      </c>
+      <c r="C19" s="38">
+        <v>31</v>
+      </c>
+      <c r="D19" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="38">
+        <v>56</v>
+      </c>
+      <c r="C20" s="38">
+        <v>73</v>
+      </c>
+      <c r="D20" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="B21" s="38">
+        <v>39</v>
+      </c>
+      <c r="C21" s="38">
+        <v>31</v>
+      </c>
+      <c r="D21" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="B22" s="38">
+        <v>59</v>
+      </c>
+      <c r="C22" s="38">
+        <v>43</v>
+      </c>
+      <c r="D22" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="B23" s="38">
+        <v>45</v>
+      </c>
+      <c r="C23" s="38">
+        <v>88</v>
+      </c>
+      <c r="D23" s="38" t="str">
+        <f t="shared" si="1"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="B24" s="38">
+        <v>38</v>
+      </c>
+      <c r="C24" s="38">
+        <v>72</v>
+      </c>
+      <c r="D24" s="38"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="40"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="39"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9245F8C6-C50C-4C60-AEF8-0390BE8DB560}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="56" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="38">
+        <v>1</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="38">
+        <v>12</v>
+      </c>
+      <c r="D3" s="38" t="str">
+        <f>IF(C3&gt;=40,"PASS","FAIL")</f>
+        <v>FAIL</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="38">
+        <v>2</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="38">
+        <v>5</v>
+      </c>
+      <c r="D4" s="38" t="str">
+        <f t="shared" ref="D4:D22" si="0">IF(C4&gt;=40,"PASS","FAIL")</f>
+        <v>FAIL</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="38">
+        <v>3</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="38">
+        <v>21</v>
+      </c>
+      <c r="D5" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>FAIL</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="38">
+        <v>4</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="38">
+        <v>36</v>
+      </c>
+      <c r="D6" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>FAIL</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="38">
+        <v>5</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="38">
+        <v>38</v>
+      </c>
+      <c r="D7" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>FAIL</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="38">
+        <v>6</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="38">
+        <v>68</v>
+      </c>
+      <c r="D8" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="38">
+        <v>7</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="38">
+        <v>63</v>
+      </c>
+      <c r="D9" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="38">
+        <v>8</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="38">
+        <v>72</v>
+      </c>
+      <c r="D10" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="38">
+        <v>9</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="38">
+        <v>72</v>
+      </c>
+      <c r="D11" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="38">
+        <v>10</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="38">
+        <v>20</v>
+      </c>
+      <c r="D12" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>FAIL</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="38">
+        <v>11</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="38">
+        <v>83</v>
+      </c>
+      <c r="D13" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="38">
+        <v>12</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="38">
+        <v>56</v>
+      </c>
+      <c r="D14" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="38">
+        <v>13</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="38">
+        <v>20</v>
+      </c>
+      <c r="D15" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>FAIL</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="38">
+        <v>14</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="38">
+        <v>95</v>
+      </c>
+      <c r="D16" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="38">
+        <v>15</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="38">
+        <v>52</v>
+      </c>
+      <c r="D17" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="38">
+        <v>16</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="38">
+        <v>11</v>
+      </c>
+      <c r="D18" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>FAIL</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="38">
+        <v>17</v>
+      </c>
+      <c r="B19" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="38">
+        <v>6</v>
+      </c>
+      <c r="D19" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>FAIL</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="38">
+        <v>18</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="38">
+        <v>100</v>
+      </c>
+      <c r="D20" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="38">
+        <v>19</v>
+      </c>
+      <c r="B21" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="38">
+        <v>82</v>
+      </c>
+      <c r="D21" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="38">
+        <v>20</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="38">
+        <v>91</v>
+      </c>
+      <c r="D22" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A795878E-79ED-4055-AF18-22E4BA6B9D67}">
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="38" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" s="45">
+        <v>43436</v>
+      </c>
+      <c r="C3" s="38" t="str">
+        <f>IF(B3&gt;=40000,"Bonus","No Bonus")</f>
+        <v>Bonus</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="45">
+        <v>28722</v>
+      </c>
+      <c r="C4" s="38" t="str">
+        <f t="shared" ref="C4:C22" si="0">IF(B4&gt;=40000,"Bonus","No Bonus")</f>
+        <v>No Bonus</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="45">
+        <v>39668</v>
+      </c>
+      <c r="C5" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>No Bonus</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" s="45">
+        <v>52001</v>
+      </c>
+      <c r="C6" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Bonus</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="38" t="s">
+        <v>199</v>
+      </c>
+      <c r="B7" s="45">
+        <v>67573</v>
+      </c>
+      <c r="C7" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Bonus</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="45">
+        <v>67420</v>
+      </c>
+      <c r="C8" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Bonus</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" s="45">
+        <v>58697</v>
+      </c>
+      <c r="C9" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Bonus</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="B10" s="45">
+        <v>17690</v>
+      </c>
+      <c r="C10" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>No Bonus</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" s="45">
+        <v>50802</v>
+      </c>
+      <c r="C11" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Bonus</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="45">
+        <v>69460</v>
+      </c>
+      <c r="C12" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Bonus</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" s="45">
+        <v>26751</v>
+      </c>
+      <c r="C13" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>No Bonus</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" s="45">
+        <v>27476</v>
+      </c>
+      <c r="C14" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>No Bonus</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="45">
+        <v>52487</v>
+      </c>
+      <c r="C15" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Bonus</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="45">
+        <v>68932</v>
+      </c>
+      <c r="C16" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Bonus</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" s="45">
+        <v>51620</v>
+      </c>
+      <c r="C17" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Bonus</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="B18" s="45">
+        <v>25102</v>
+      </c>
+      <c r="C18" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>No Bonus</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="B19" s="45">
+        <v>45251</v>
+      </c>
+      <c r="C19" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Bonus</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="B20" s="45">
+        <v>58426</v>
+      </c>
+      <c r="C20" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Bonus</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="B21" s="45">
+        <v>61364</v>
+      </c>
+      <c r="C21" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Bonus</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="B22" s="45">
+        <v>64437</v>
+      </c>
+      <c r="C22" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Bonus</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C02F432-FCE8-4F64-9BC7-8C5F0E6B0EC2}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="38">
+        <v>1</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="38">
+        <v>12</v>
+      </c>
+      <c r="D3" s="38" t="str">
+        <f>IF(C3&gt;70,"A",IF(C3&gt;60,"B",IF(C3&gt;=40,"C","Fail")))</f>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="38">
+        <v>2</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="38">
+        <v>5</v>
+      </c>
+      <c r="D4" s="38" t="str">
+        <f t="shared" ref="D4:D22" si="0">IF(C4&gt;70,"A",IF(C4&gt;60,"B",IF(C4&gt;=40,"C","Fail")))</f>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="38">
+        <v>3</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="38">
+        <v>21</v>
+      </c>
+      <c r="D5" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="38">
+        <v>4</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="38">
+        <v>36</v>
+      </c>
+      <c r="D6" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="38">
+        <v>5</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="38">
+        <v>38</v>
+      </c>
+      <c r="D7" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="38">
+        <v>6</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="38">
+        <v>68</v>
+      </c>
+      <c r="D8" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="38">
+        <v>7</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="38">
+        <v>63</v>
+      </c>
+      <c r="D9" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>B</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="38">
+        <v>8</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="38">
+        <v>72</v>
+      </c>
+      <c r="D10" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="38">
+        <v>9</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="38">
+        <v>72</v>
+      </c>
+      <c r="D11" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="38">
+        <v>10</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="38">
+        <v>20</v>
+      </c>
+      <c r="D12" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="38">
+        <v>11</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="38">
+        <v>83</v>
+      </c>
+      <c r="D13" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="38">
+        <v>12</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="38">
+        <v>56</v>
+      </c>
+      <c r="D14" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>C</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="38">
+        <v>13</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="38">
+        <v>20</v>
+      </c>
+      <c r="D15" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="38">
+        <v>14</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="38">
+        <v>95</v>
+      </c>
+      <c r="D16" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="38">
+        <v>15</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="38">
+        <v>52</v>
+      </c>
+      <c r="D17" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>C</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="38">
+        <v>16</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="38">
+        <v>11</v>
+      </c>
+      <c r="D18" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="38">
+        <v>17</v>
+      </c>
+      <c r="B19" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="38">
+        <v>6</v>
+      </c>
+      <c r="D19" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="38">
+        <v>18</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="38">
+        <v>100</v>
+      </c>
+      <c r="D20" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="38">
+        <v>19</v>
+      </c>
+      <c r="B21" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="38">
+        <v>82</v>
+      </c>
+      <c r="D21" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="38">
+        <v>20</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="38">
+        <v>91</v>
+      </c>
+      <c r="D22" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>A</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86EFEFD-611C-4832-BDF7-61F66AD2311B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{390279AE-8DB3-4F4A-994A-B7612B4C7846}">
+  <dimension ref="A2:D22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="38">
+        <v>38</v>
+      </c>
+      <c r="C3" s="38">
+        <v>5</v>
+      </c>
+      <c r="D3" s="38" t="str">
+        <f>IF(AND(B3&gt;21,C3&gt;=1),"Eligible","Not Eligible")</f>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="38">
+        <v>33</v>
+      </c>
+      <c r="C4" s="38">
+        <v>4</v>
+      </c>
+      <c r="D4" s="38" t="str">
+        <f t="shared" ref="D4:D22" si="0">IF(AND(B4&gt;21,C4&gt;=1),"Eligible","Not Eligible")</f>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="38">
+        <v>36</v>
+      </c>
+      <c r="C5" s="38">
+        <v>6</v>
+      </c>
+      <c r="D5" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="38">
+        <v>33</v>
+      </c>
+      <c r="C6" s="38">
+        <v>5</v>
+      </c>
+      <c r="D6" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="38">
+        <v>27</v>
+      </c>
+      <c r="C7" s="38">
+        <v>1</v>
+      </c>
+      <c r="D7" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="38">
+        <v>28</v>
+      </c>
+      <c r="C8" s="38">
+        <v>0</v>
+      </c>
+      <c r="D8" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="38">
+        <v>23</v>
+      </c>
+      <c r="C9" s="38">
+        <v>2</v>
+      </c>
+      <c r="D9" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="38">
+        <v>32</v>
+      </c>
+      <c r="C10" s="38">
+        <v>6</v>
+      </c>
+      <c r="D10" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="38">
+        <v>33</v>
+      </c>
+      <c r="C11" s="38">
+        <v>4</v>
+      </c>
+      <c r="D11" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="38">
+        <v>34</v>
+      </c>
+      <c r="C12" s="38">
+        <v>4</v>
+      </c>
+      <c r="D12" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="38">
+        <v>31</v>
+      </c>
+      <c r="C13" s="38">
+        <v>0</v>
+      </c>
+      <c r="D13" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="38">
+        <v>34</v>
+      </c>
+      <c r="C14" s="38">
+        <v>0</v>
+      </c>
+      <c r="D14" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="38">
+        <v>39</v>
+      </c>
+      <c r="C15" s="38">
+        <v>0</v>
+      </c>
+      <c r="D15" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="38">
+        <v>26</v>
+      </c>
+      <c r="C16" s="38">
+        <v>1</v>
+      </c>
+      <c r="D16" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="38">
+        <v>26</v>
+      </c>
+      <c r="C17" s="38">
+        <v>1</v>
+      </c>
+      <c r="D17" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="38">
+        <v>38</v>
+      </c>
+      <c r="C18" s="38">
+        <v>0</v>
+      </c>
+      <c r="D18" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="38">
+        <v>25</v>
+      </c>
+      <c r="C19" s="38">
+        <v>0</v>
+      </c>
+      <c r="D19" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="38">
+        <v>29</v>
+      </c>
+      <c r="C20" s="38">
+        <v>0</v>
+      </c>
+      <c r="D20" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eligible</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="38">
+        <v>25</v>
+      </c>
+      <c r="C21" s="38">
+        <v>3</v>
+      </c>
+      <c r="D21" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="38">
+        <v>33</v>
+      </c>
+      <c r="C22" s="38">
+        <v>2</v>
+      </c>
+      <c r="D22" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD54CCEC-5E96-4B7C-B658-0365A7AFB75A}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="38">
+        <v>30</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="38" t="str">
+        <f>IF(AND(B3&gt;=75,C3="Yes"),"Eligible","Not Eliigible")</f>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="38">
+        <v>57</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" s="38" t="str">
+        <f t="shared" ref="D4:D22" si="0">IF(AND(B4&gt;=75,C4="Yes"),"Eligible","Not Eliigible")</f>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="38">
+        <v>35</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D5" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="38">
+        <v>64</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D6" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="38">
+        <v>24</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D7" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="38">
+        <v>29</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D8" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="38">
+        <v>53</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D9" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="38">
+        <v>42</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="38">
+        <v>31</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D11" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="38">
+        <v>48</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="38">
+        <v>78</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D13" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="38">
+        <v>28</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D14" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="38">
+        <v>30</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D15" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="38">
+        <v>80</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D16" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Eligible</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="38">
+        <v>60</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D17" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="38">
+        <v>94</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D18" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="38">
+        <v>53</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D19" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="38">
+        <v>60</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D20" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="38">
+        <v>22</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D21" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="38">
+        <v>51</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D22" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Eliigible</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C31A0BAB-5647-41F8-B7B9-429963493A92}">
+  <dimension ref="A2:D22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>224</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" s="38">
+        <v>43376</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="38">
+        <v>18791</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="38">
+        <v>25549</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" s="38">
+        <v>10806</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="38" t="s">
+        <v>199</v>
+      </c>
+      <c r="B7" s="38">
+        <v>23014</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D7" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="38">
+        <v>6395</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" s="38">
+        <v>44288</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="B10" s="38">
+        <v>11710</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" s="38">
+        <v>17439</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="38">
+        <v>48739</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" s="38">
+        <v>11685</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" s="38">
+        <v>28741</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="38">
+        <v>18312</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="38">
+        <v>9275</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" s="38">
+        <v>22051</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="B18" s="38">
+        <v>21399</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="B19" s="38">
+        <v>45082</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D19" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="B20" s="38">
+        <v>33820</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="B21" s="38">
+        <v>44928</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="B22" s="38">
+        <v>38914</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>225</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF3B9DB-AD58-4243-A3CB-79D8E11F9857}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.109375" style="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" style="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.21875" style="32" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="32"/>
+    <col min="1" max="1" width="15.140625" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" style="32" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
@@ -1965,20 +4987,20 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="46" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="37"/>
+      <c r="B23" s="46"/>
       <c r="C23" s="35">
         <f>SUMIF(B3:B22,"IT",C3:C22)</f>
         <v>223661</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="B24" s="39"/>
+      <c r="B24" s="48"/>
       <c r="C24" s="35">
         <f>SUMIF(B3:B22,"HR",C3:C22)</f>
         <v>208692</v>
@@ -1987,10 +5009,10 @@
       <c r="F24" s="33"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="46" t="s">
         <v>110</v>
       </c>
-      <c r="B25" s="37"/>
+      <c r="B25" s="46"/>
       <c r="C25" s="35">
         <f>SUMIF(B3:B22,"FINANCE",C3:C22)</f>
         <v>338098</v>
@@ -1999,20 +5021,20 @@
       <c r="F25" s="33"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="46" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="37"/>
+      <c r="B26" s="46"/>
       <c r="C26" s="35">
         <f>AVERAGE(C3:C22)</f>
         <v>38522.550000000003</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="B27" s="37"/>
+      <c r="B27" s="46"/>
       <c r="C27" s="35">
         <f>COUNTA(A3:A22)</f>
         <v>20</v>
@@ -2031,27 +5053,1219 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A951C976-7A73-4F41-A8E3-818E30E3A4BC}">
+  <dimension ref="A2:D22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" s="38">
+        <v>43376</v>
+      </c>
+      <c r="C3" s="38">
+        <v>727</v>
+      </c>
+      <c r="D3" s="38" t="str">
+        <f>IF(OR(B3&gt;40000,C3&gt;=700),"Approved","Not Approved")</f>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="38">
+        <v>18791</v>
+      </c>
+      <c r="C4" s="38">
+        <v>617</v>
+      </c>
+      <c r="D4" s="38" t="str">
+        <f t="shared" ref="D4:D22" si="0">IF(OR(B4&gt;40000,C4&gt;=700),"Approved","Not Approved")</f>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="38">
+        <v>25549</v>
+      </c>
+      <c r="C5" s="38">
+        <v>701</v>
+      </c>
+      <c r="D5" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" s="38">
+        <v>10806</v>
+      </c>
+      <c r="C6" s="38">
+        <v>724</v>
+      </c>
+      <c r="D6" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="38" t="s">
+        <v>199</v>
+      </c>
+      <c r="B7" s="38">
+        <v>23014</v>
+      </c>
+      <c r="C7" s="38">
+        <v>718</v>
+      </c>
+      <c r="D7" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="38">
+        <v>6395</v>
+      </c>
+      <c r="C8" s="38">
+        <v>755</v>
+      </c>
+      <c r="D8" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" s="38">
+        <v>44288</v>
+      </c>
+      <c r="C9" s="38">
+        <v>738</v>
+      </c>
+      <c r="D9" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="B10" s="38">
+        <v>11710</v>
+      </c>
+      <c r="C10" s="38">
+        <v>744</v>
+      </c>
+      <c r="D10" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" s="38">
+        <v>17439</v>
+      </c>
+      <c r="C11" s="38">
+        <v>779</v>
+      </c>
+      <c r="D11" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="38">
+        <v>48739</v>
+      </c>
+      <c r="C12" s="38">
+        <v>666</v>
+      </c>
+      <c r="D12" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" s="38">
+        <v>11685</v>
+      </c>
+      <c r="C13" s="38">
+        <v>708</v>
+      </c>
+      <c r="D13" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" s="38">
+        <v>28741</v>
+      </c>
+      <c r="C14" s="38">
+        <v>600</v>
+      </c>
+      <c r="D14" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="38">
+        <v>18312</v>
+      </c>
+      <c r="C15" s="38">
+        <v>759</v>
+      </c>
+      <c r="D15" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="38">
+        <v>9275</v>
+      </c>
+      <c r="C16" s="38">
+        <v>703</v>
+      </c>
+      <c r="D16" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" s="38">
+        <v>22051</v>
+      </c>
+      <c r="C17" s="38">
+        <v>660</v>
+      </c>
+      <c r="D17" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="B18" s="38">
+        <v>21399</v>
+      </c>
+      <c r="C18" s="38">
+        <v>704</v>
+      </c>
+      <c r="D18" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="B19" s="38">
+        <v>45082</v>
+      </c>
+      <c r="C19" s="38">
+        <v>786</v>
+      </c>
+      <c r="D19" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="B20" s="38">
+        <v>33820</v>
+      </c>
+      <c r="C20" s="38">
+        <v>661</v>
+      </c>
+      <c r="D20" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="B21" s="38">
+        <v>44928</v>
+      </c>
+      <c r="C21" s="38">
+        <v>713</v>
+      </c>
+      <c r="D21" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Approved</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="B22" s="38">
+        <v>38914</v>
+      </c>
+      <c r="C22" s="38">
+        <v>619</v>
+      </c>
+      <c r="D22" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Approved</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0D66E1-E774-4B2C-A9FE-22C895D8D2E8}">
+  <dimension ref="A2:C22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="38" t="s">
+        <v>199</v>
+      </c>
+      <c r="B7" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="B10" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="B18" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="B19" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="B20" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="B21" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="B22" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>234</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63AFD9D4-E5C4-479F-BB15-CE55F2F6602E}">
+  <dimension ref="A2:C23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="38">
+        <v>14</v>
+      </c>
+      <c r="B3" s="38">
+        <v>17</v>
+      </c>
+      <c r="C3" s="44">
+        <f>IFERROR(A3/B3,"Invalid")</f>
+        <v>0.82352941176470584</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="38">
+        <v>8</v>
+      </c>
+      <c r="B4" s="38">
+        <v>46</v>
+      </c>
+      <c r="C4" s="44">
+        <f t="shared" ref="C4:C23" si="0">IFERROR(A4/B4,"Invalid")</f>
+        <v>0.17391304347826086</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="38">
+        <v>9</v>
+      </c>
+      <c r="B5" s="38">
+        <v>20</v>
+      </c>
+      <c r="C5" s="44">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="38">
+        <v>40</v>
+      </c>
+      <c r="B6" s="38">
+        <v>43</v>
+      </c>
+      <c r="C6" s="44">
+        <f t="shared" si="0"/>
+        <v>0.93023255813953487</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="38">
+        <v>42</v>
+      </c>
+      <c r="B7" s="38">
+        <v>48</v>
+      </c>
+      <c r="C7" s="44">
+        <f t="shared" si="0"/>
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="38">
+        <v>38</v>
+      </c>
+      <c r="B8" s="38">
+        <v>10</v>
+      </c>
+      <c r="C8" s="44">
+        <f t="shared" si="0"/>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="38">
+        <v>13</v>
+      </c>
+      <c r="B9" s="38">
+        <v>20</v>
+      </c>
+      <c r="C9" s="44">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="38">
+        <v>5</v>
+      </c>
+      <c r="B10" s="38">
+        <v>0</v>
+      </c>
+      <c r="C10" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>Invalid</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="38">
+        <v>41</v>
+      </c>
+      <c r="B11" s="38">
+        <v>9</v>
+      </c>
+      <c r="C11" s="44">
+        <f t="shared" si="0"/>
+        <v>4.5555555555555554</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="38">
+        <v>1</v>
+      </c>
+      <c r="B12" s="38">
+        <v>22</v>
+      </c>
+      <c r="C12" s="44">
+        <f t="shared" si="0"/>
+        <v>4.5454545454545456E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="38">
+        <v>26</v>
+      </c>
+      <c r="B13" s="38">
+        <v>22</v>
+      </c>
+      <c r="C13" s="44">
+        <f t="shared" si="0"/>
+        <v>1.1818181818181819</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="38">
+        <v>49</v>
+      </c>
+      <c r="B14" s="38">
+        <v>18</v>
+      </c>
+      <c r="C14" s="44">
+        <f t="shared" si="0"/>
+        <v>2.7222222222222223</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="38">
+        <v>35</v>
+      </c>
+      <c r="B15" s="38">
+        <v>0</v>
+      </c>
+      <c r="C15" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>Invalid</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="38">
+        <v>19</v>
+      </c>
+      <c r="B16" s="38">
+        <v>30</v>
+      </c>
+      <c r="C16" s="44">
+        <f t="shared" si="0"/>
+        <v>0.6333333333333333</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="38">
+        <v>34</v>
+      </c>
+      <c r="B17" s="38">
+        <v>27</v>
+      </c>
+      <c r="C17" s="44">
+        <f t="shared" si="0"/>
+        <v>1.2592592592592593</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="38">
+        <v>28</v>
+      </c>
+      <c r="B18" s="38">
+        <v>2</v>
+      </c>
+      <c r="C18" s="44">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="38">
+        <v>5</v>
+      </c>
+      <c r="B19" s="38">
+        <v>33</v>
+      </c>
+      <c r="C19" s="44">
+        <f t="shared" si="0"/>
+        <v>0.15151515151515152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="38">
+        <v>35</v>
+      </c>
+      <c r="B20" s="38">
+        <v>9</v>
+      </c>
+      <c r="C20" s="44">
+        <f t="shared" si="0"/>
+        <v>3.8888888888888888</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="38">
+        <v>31</v>
+      </c>
+      <c r="B21" s="38">
+        <v>20</v>
+      </c>
+      <c r="C21" s="44">
+        <f t="shared" si="0"/>
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="38">
+        <v>7</v>
+      </c>
+      <c r="B22" s="38">
+        <v>0</v>
+      </c>
+      <c r="C22" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>Invalid</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="38">
+        <v>4</v>
+      </c>
+      <c r="B23" s="38">
+        <v>40</v>
+      </c>
+      <c r="C23" s="44">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F73A591B-1E6A-4357-82C0-BBAB7B9A707D}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>237</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" s="38">
+        <v>36</v>
+      </c>
+      <c r="C3" s="38">
+        <v>72</v>
+      </c>
+      <c r="D3" s="38" t="str">
+        <f>IF(AND(C3&gt;=90,B3&gt;=40),"EXCELLENT",IF(C3&gt;=80,"Good","Needs Improvement"))</f>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="38">
+        <v>30</v>
+      </c>
+      <c r="C4" s="38">
+        <v>94</v>
+      </c>
+      <c r="D4" s="38" t="str">
+        <f t="shared" ref="D4:D22" si="0">IF(AND(C4&gt;=90,B4&gt;=40),"EXCELLENT",IF(C4&gt;=80,"Good","Needs Improvement"))</f>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="38">
+        <v>54</v>
+      </c>
+      <c r="C5" s="38">
+        <v>73</v>
+      </c>
+      <c r="D5" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" s="38">
+        <v>39</v>
+      </c>
+      <c r="C6" s="38">
+        <v>80</v>
+      </c>
+      <c r="D6" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="38" t="s">
+        <v>199</v>
+      </c>
+      <c r="B7" s="38">
+        <v>35</v>
+      </c>
+      <c r="C7" s="38">
+        <v>80</v>
+      </c>
+      <c r="D7" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="38">
+        <v>50</v>
+      </c>
+      <c r="C8" s="38">
+        <v>86</v>
+      </c>
+      <c r="D8" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" s="38">
+        <v>54</v>
+      </c>
+      <c r="C9" s="38">
+        <v>78</v>
+      </c>
+      <c r="D9" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="B10" s="38">
+        <v>49</v>
+      </c>
+      <c r="C10" s="38">
+        <v>99</v>
+      </c>
+      <c r="D10" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>EXCELLENT</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" s="38">
+        <v>38</v>
+      </c>
+      <c r="C11" s="38">
+        <v>65</v>
+      </c>
+      <c r="D11" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="38">
+        <v>51</v>
+      </c>
+      <c r="C12" s="38">
+        <v>83</v>
+      </c>
+      <c r="D12" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" s="38">
+        <v>53</v>
+      </c>
+      <c r="C13" s="38">
+        <v>73</v>
+      </c>
+      <c r="D13" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" s="38">
+        <v>27</v>
+      </c>
+      <c r="C14" s="38">
+        <v>91</v>
+      </c>
+      <c r="D14" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="38">
+        <v>23</v>
+      </c>
+      <c r="C15" s="38">
+        <v>88</v>
+      </c>
+      <c r="D15" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="38">
+        <v>20</v>
+      </c>
+      <c r="C16" s="38">
+        <v>61</v>
+      </c>
+      <c r="D16" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" s="38">
+        <v>35</v>
+      </c>
+      <c r="C17" s="38">
+        <v>42</v>
+      </c>
+      <c r="D17" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="B18" s="38">
+        <v>60</v>
+      </c>
+      <c r="C18" s="38">
+        <v>81</v>
+      </c>
+      <c r="D18" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="B19" s="38">
+        <v>51</v>
+      </c>
+      <c r="C19" s="38">
+        <v>97</v>
+      </c>
+      <c r="D19" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>EXCELLENT</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="B20" s="38">
+        <v>57</v>
+      </c>
+      <c r="C20" s="38">
+        <v>49</v>
+      </c>
+      <c r="D20" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="B21" s="38">
+        <v>38</v>
+      </c>
+      <c r="C21" s="38">
+        <v>45</v>
+      </c>
+      <c r="D21" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Needs Improvement</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="B22" s="38">
+        <v>40</v>
+      </c>
+      <c r="C22" s="38">
+        <v>80</v>
+      </c>
+      <c r="D22" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Good</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BFDBEE5-CB8F-49C5-9FDB-FB34A20A3D23}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.109375" style="11"/>
+    <col min="3" max="3" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:5" ht="25.5" x14ac:dyDescent="0.5">
+      <c r="A1" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>48</v>
       </c>
@@ -2066,7 +6280,7 @@
       </c>
       <c r="E2" s="12"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>58</v>
       </c>
@@ -2080,7 +6294,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>58</v>
       </c>
@@ -2094,7 +6308,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="38.4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" ht="34.5" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>61</v>
       </c>
@@ -2108,7 +6322,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>58</v>
       </c>
@@ -2122,7 +6336,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="38.4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" ht="34.5" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>61</v>
       </c>
@@ -2136,7 +6350,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>52</v>
       </c>
@@ -2150,7 +6364,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>58</v>
       </c>
@@ -2164,7 +6378,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>52</v>
       </c>
@@ -2178,7 +6392,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>52</v>
       </c>
@@ -2192,7 +6406,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>55</v>
       </c>
@@ -2206,7 +6420,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>58</v>
       </c>
@@ -2220,7 +6434,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>55</v>
       </c>
@@ -2234,7 +6448,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>52</v>
       </c>
@@ -2248,7 +6462,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>55</v>
       </c>
@@ -2262,7 +6476,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>58</v>
       </c>
@@ -2276,7 +6490,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>55</v>
       </c>
@@ -2290,7 +6504,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>52</v>
       </c>
@@ -2304,7 +6518,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>52</v>
       </c>
@@ -2318,7 +6532,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>52</v>
       </c>
@@ -2343,30 +6557,30 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AF3328-C6E1-4004-AA50-86F5408E7E6C}">
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="10"/>
+    <col min="6" max="6" width="6.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>65</v>
       </c>
@@ -2389,7 +6603,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A3" s="22">
         <v>1</v>
       </c>
@@ -2414,7 +6628,7 @@
         <v>57.333333333333336</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A4" s="22">
         <v>2</v>
       </c>
@@ -2439,7 +6653,7 @@
         <v>43.666666666666664</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A5" s="22">
         <v>3</v>
       </c>
@@ -2464,7 +6678,7 @@
         <v>41.666666666666664</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A6" s="22">
         <v>4</v>
       </c>
@@ -2489,7 +6703,7 @@
         <v>30.333333333333332</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A7" s="22">
         <v>5</v>
       </c>
@@ -2514,7 +6728,7 @@
         <v>49.666666666666664</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A8" s="22">
         <v>6</v>
       </c>
@@ -2539,7 +6753,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A9" s="22">
         <v>7</v>
       </c>
@@ -2564,7 +6778,7 @@
         <v>56.666666666666664</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A10" s="22">
         <v>8</v>
       </c>
@@ -2589,7 +6803,7 @@
         <v>48.666666666666664</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A11" s="22">
         <v>9</v>
       </c>
@@ -2614,7 +6828,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A12" s="22">
         <v>10</v>
       </c>
@@ -2639,7 +6853,7 @@
         <v>23.333333333333332</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A13" s="22">
         <v>11</v>
       </c>
@@ -2664,7 +6878,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A14" s="22">
         <v>12</v>
       </c>
@@ -2689,7 +6903,7 @@
         <v>40.333333333333336</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A15" s="22">
         <v>13</v>
       </c>
@@ -2714,7 +6928,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A16" s="22">
         <v>14</v>
       </c>
@@ -2739,7 +6953,7 @@
         <v>63.333333333333336</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A17" s="22">
         <v>15</v>
       </c>
@@ -2764,7 +6978,7 @@
         <v>63.333333333333336</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A18" s="22">
         <v>16</v>
       </c>
@@ -2789,7 +7003,7 @@
         <v>56.666666666666664</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A19" s="22">
         <v>17</v>
       </c>
@@ -2814,7 +7028,7 @@
         <v>37.333333333333336</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A20" s="22">
         <v>18</v>
       </c>
@@ -2839,7 +7053,7 @@
         <v>49.666666666666664</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A21" s="22">
         <v>19</v>
       </c>
@@ -2864,7 +7078,7 @@
         <v>47.333333333333336</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="19.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A22" s="22">
         <v>20</v>
       </c>
@@ -2900,22 +7114,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB224D9D-D235-4595-95E9-D4BEE2872F02}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.109375" style="10"/>
+    <col min="1" max="1" width="11.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>74</v>
       </c>
@@ -2926,7 +7140,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>77</v>
       </c>
@@ -2935,14 +7149,14 @@
       </c>
       <c r="C3" s="31">
         <f ca="1">RANDBETWEEN(10000,50000)</f>
-        <v>33483</v>
+        <v>34787</v>
       </c>
       <c r="D3" s="25"/>
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
       <c r="G3" s="25"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>78</v>
       </c>
@@ -2951,10 +7165,10 @@
       </c>
       <c r="C4" s="31">
         <f t="shared" ref="C4:C22" ca="1" si="0">RANDBETWEEN(10000,50000)</f>
-        <v>25137</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>42613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
         <v>79</v>
       </c>
@@ -2963,10 +7177,10 @@
       </c>
       <c r="C5" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>22236</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>17397</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>80</v>
       </c>
@@ -2975,10 +7189,10 @@
       </c>
       <c r="C6" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>26343</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>39203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>81</v>
       </c>
@@ -2987,10 +7201,10 @@
       </c>
       <c r="C7" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>35969</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>24189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
         <v>82</v>
       </c>
@@ -2999,10 +7213,10 @@
       </c>
       <c r="C8" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>15561</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>27022</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>83</v>
       </c>
@@ -3011,10 +7225,10 @@
       </c>
       <c r="C9" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>18723</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12365</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>84</v>
       </c>
@@ -3023,10 +7237,10 @@
       </c>
       <c r="C10" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>36949</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>45656</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>85</v>
       </c>
@@ -3035,10 +7249,10 @@
       </c>
       <c r="C11" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>47480</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>24345</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
         <v>86</v>
       </c>
@@ -3047,10 +7261,10 @@
       </c>
       <c r="C12" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>33024</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>41852</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>87</v>
       </c>
@@ -3059,10 +7273,10 @@
       </c>
       <c r="C13" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>16895</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>16039</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
         <v>88</v>
       </c>
@@ -3071,10 +7285,10 @@
       </c>
       <c r="C14" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>37352</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>41975</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>89</v>
       </c>
@@ -3083,10 +7297,10 @@
       </c>
       <c r="C15" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>42452</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>25846</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
         <v>90</v>
       </c>
@@ -3095,10 +7309,10 @@
       </c>
       <c r="C16" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>13521</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+        <v>32747</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
         <v>91</v>
       </c>
@@ -3107,10 +7321,10 @@
       </c>
       <c r="C17" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>36164</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>27324</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
         <v>92</v>
       </c>
@@ -3119,10 +7333,10 @@
       </c>
       <c r="C18" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>26643</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>44036</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
         <v>93</v>
       </c>
@@ -3131,10 +7345,10 @@
       </c>
       <c r="C19" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>35988</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>43738</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
         <v>94</v>
       </c>
@@ -3143,10 +7357,10 @@
       </c>
       <c r="C20" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>46958</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>35915</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>95</v>
       </c>
@@ -3155,10 +7369,10 @@
       </c>
       <c r="C21" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>49659</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+        <v>22265</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
         <v>96</v>
       </c>
@@ -3167,47 +7381,47 @@
       </c>
       <c r="C22" s="31">
         <f t="shared" ca="1" si="0"/>
-        <v>34142</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="43" t="s">
+        <v>36429</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="43"/>
+      <c r="B23" s="52"/>
       <c r="C23" s="31">
         <f ca="1">SUM(C3:C22)</f>
-        <v>634679</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="43" t="s">
+        <v>635743</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="B24" s="43"/>
+      <c r="B24" s="52"/>
       <c r="C24" s="31">
         <f ca="1">AVERAGE(C3:C22)</f>
-        <v>31733.95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="43" t="s">
+        <v>31787.15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="43"/>
+      <c r="B25" s="52"/>
       <c r="C25" s="31">
         <f ca="1">MAX(C3:C22)</f>
-        <v>49659</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="43" t="s">
+        <v>45656</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="B26" s="43"/>
+      <c r="B26" s="52"/>
       <c r="C26" s="31">
         <f ca="1">MIN(C3:C22)</f>
-        <v>13521</v>
+        <v>12365</v>
       </c>
     </row>
   </sheetData>
@@ -3226,28 +7440,28 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C0707F-133D-4C16-8F71-A0EBF05D58AA}">
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="6.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="10"/>
+    <col min="1" max="1" width="18.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="6.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
       <c r="G1" s="22"/>
       <c r="H1" s="22"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>66</v>
       </c>
@@ -3273,7 +7487,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>6</v>
       </c>
@@ -3301,7 +7515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>9</v>
       </c>
@@ -3329,7 +7543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
         <v>12</v>
       </c>
@@ -3357,7 +7571,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>14</v>
       </c>
@@ -3385,7 +7599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>16</v>
       </c>
@@ -3413,7 +7627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
         <v>32</v>
       </c>
@@ -3441,7 +7655,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>33</v>
       </c>
@@ -3469,7 +7683,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>34</v>
       </c>
@@ -3497,7 +7711,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>35</v>
       </c>
@@ -3525,7 +7739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
         <v>36</v>
       </c>
@@ -3553,7 +7767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>37</v>
       </c>
@@ -3581,7 +7795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
         <v>38</v>
       </c>
@@ -3609,7 +7823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>39</v>
       </c>
@@ -3637,7 +7851,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
         <v>40</v>
       </c>
@@ -3665,7 +7879,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
         <v>41</v>
       </c>
@@ -3693,7 +7907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
         <v>42</v>
       </c>
@@ -3721,7 +7935,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
         <v>43</v>
       </c>
@@ -3749,7 +7963,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
         <v>44</v>
       </c>
@@ -3777,7 +7991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>45</v>
       </c>
@@ -3805,7 +8019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
         <v>46</v>
       </c>
@@ -3845,20 +8059,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D136D3B8-76A6-43E7-8CE5-A7F172BA31A5}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="10"/>
+    <col min="1" max="1" width="12.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.85546875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="53" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="44"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B1" s="53"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>123</v>
       </c>
@@ -3866,7 +8080,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>124</v>
       </c>
@@ -3874,7 +8088,7 @@
         <v>10217</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>125</v>
       </c>
@@ -3882,7 +8096,7 @@
         <v>16301</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
         <v>126</v>
       </c>
@@ -3890,7 +8104,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>127</v>
       </c>
@@ -3898,7 +8112,7 @@
         <v>5271</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>128</v>
       </c>
@@ -3906,7 +8120,7 @@
         <v>21344</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
         <v>129</v>
       </c>
@@ -3914,7 +8128,7 @@
         <v>4420</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>130</v>
       </c>
@@ -3922,7 +8136,7 @@
         <v>27119</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>131</v>
       </c>
@@ -3930,7 +8144,7 @@
         <v>18351</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>132</v>
       </c>
@@ -3938,7 +8152,7 @@
         <v>18216</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
         <v>133</v>
       </c>
@@ -3946,7 +8160,7 @@
         <v>6339</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>134</v>
       </c>
@@ -3954,7 +8168,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
         <v>135</v>
       </c>
@@ -3962,7 +8176,7 @@
         <v>15725</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>136</v>
       </c>
@@ -3970,7 +8184,7 @@
         <v>10307</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
         <v>137</v>
       </c>
@@ -3978,7 +8192,7 @@
         <v>22875</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
         <v>138</v>
       </c>
@@ -3986,7 +8200,7 @@
         <v>5074</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
         <v>139</v>
       </c>
@@ -3994,7 +8208,7 @@
         <v>20772</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
         <v>140</v>
       </c>
@@ -4002,7 +8216,7 @@
         <v>25310</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
         <v>141</v>
       </c>
@@ -4010,7 +8224,7 @@
         <v>21732</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>142</v>
       </c>
@@ -4018,7 +8232,7 @@
         <v>19490</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
         <v>143</v>
       </c>
@@ -4026,11 +8240,11 @@
         <v>15164</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="22"/>
       <c r="B23" s="22"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
         <v>144</v>
       </c>
@@ -4039,7 +8253,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
         <v>145</v>
       </c>
@@ -4060,20 +8274,20 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA558969-09C5-4480-A124-830A90068EE3}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" style="25" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="10"/>
+    <col min="1" max="1" width="11.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="25" customWidth="1"/>
+    <col min="3" max="16384" width="8.85546875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="54" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="45"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B1" s="54"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>147</v>
       </c>
@@ -4081,193 +8295,193 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>148</v>
       </c>
       <c r="B3" s="22">
         <f ca="1">RANDBETWEEN(500,36000)</f>
-        <v>19652</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>149</v>
       </c>
       <c r="B4" s="22">
         <f t="shared" ref="B4:B23" ca="1" si="0">RANDBETWEEN(500,36000)</f>
-        <v>30073</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>30983</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
         <v>150</v>
       </c>
       <c r="B5" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>15112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>19684</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>148</v>
       </c>
       <c r="B6" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>9360</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>19727</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>149</v>
       </c>
       <c r="B7" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>22859</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
         <v>148</v>
       </c>
       <c r="B8" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>17266</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>22309</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>149</v>
       </c>
       <c r="B9" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>18865</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+        <v>20275</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>149</v>
       </c>
       <c r="B10" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>9087</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+        <v>17787</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>151</v>
       </c>
       <c r="B11" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>25110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+        <v>33965</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
         <v>148</v>
       </c>
       <c r="B12" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>15908</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+        <v>19317</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>148</v>
       </c>
       <c r="B13" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>29127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+        <v>31113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
         <v>151</v>
       </c>
       <c r="B14" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>16002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+        <v>28965</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>149</v>
       </c>
       <c r="B15" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>4868</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>13932</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
         <v>150</v>
       </c>
       <c r="B16" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>13334</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>30370</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
         <v>151</v>
       </c>
       <c r="B17" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>17424</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
         <v>149</v>
       </c>
       <c r="B18" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>11377</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>14490</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
         <v>149</v>
       </c>
       <c r="B19" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>29279</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>29292</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
         <v>149</v>
       </c>
       <c r="B20" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>805</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7768</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>149</v>
       </c>
       <c r="B21" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>3988</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+        <v>10711</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
         <v>152</v>
       </c>
       <c r="B22" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>23557</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>35490</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
         <v>152</v>
       </c>
       <c r="B23" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>34446</v>
+        <v>2176</v>
       </c>
     </row>
   </sheetData>
@@ -4289,21 +8503,21 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F937797-AAA8-490E-96DE-B2BB904D5E31}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="10"/>
-    <col min="2" max="2" width="18.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="10"/>
+    <col min="1" max="1" width="8.85546875" style="10"/>
+    <col min="2" max="2" width="18.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.85546875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="52" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>65</v>
       </c>
@@ -4314,7 +8528,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="22">
         <v>1</v>
       </c>
@@ -4323,10 +8537,10 @@
       </c>
       <c r="C3" s="22">
         <f ca="1">RANDBETWEEN(0,100)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="22">
         <v>2</v>
       </c>
@@ -4335,10 +8549,10 @@
       </c>
       <c r="C4" s="22">
         <f t="shared" ref="C4:C22" ca="1" si="0">RANDBETWEEN(0,100)</f>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="22">
         <v>3</v>
       </c>
@@ -4347,10 +8561,10 @@
       </c>
       <c r="C5" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="22">
         <v>4</v>
       </c>
@@ -4359,10 +8573,10 @@
       </c>
       <c r="C6" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="22">
         <v>5</v>
       </c>
@@ -4371,10 +8585,10 @@
       </c>
       <c r="C7" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="22">
         <v>6</v>
       </c>
@@ -4383,10 +8597,10 @@
       </c>
       <c r="C8" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="22">
         <v>7</v>
       </c>
@@ -4395,10 +8609,10 @@
       </c>
       <c r="C9" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="22">
         <v>8</v>
       </c>
@@ -4407,10 +8621,10 @@
       </c>
       <c r="C10" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="22">
         <v>9</v>
       </c>
@@ -4419,10 +8633,10 @@
       </c>
       <c r="C11" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="22">
         <v>10</v>
       </c>
@@ -4431,10 +8645,10 @@
       </c>
       <c r="C12" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="22">
         <v>11</v>
       </c>
@@ -4443,10 +8657,10 @@
       </c>
       <c r="C13" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="22">
         <v>12</v>
       </c>
@@ -4455,10 +8669,10 @@
       </c>
       <c r="C14" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="22">
         <v>13</v>
       </c>
@@ -4467,10 +8681,10 @@
       </c>
       <c r="C15" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="22">
         <v>14</v>
       </c>
@@ -4479,10 +8693,10 @@
       </c>
       <c r="C16" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="22">
         <v>15</v>
       </c>
@@ -4491,10 +8705,10 @@
       </c>
       <c r="C17" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="22">
         <v>16</v>
       </c>
@@ -4503,10 +8717,10 @@
       </c>
       <c r="C18" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="22">
         <v>17</v>
       </c>
@@ -4515,10 +8729,10 @@
       </c>
       <c r="C19" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="22">
         <v>18</v>
       </c>
@@ -4527,10 +8741,10 @@
       </c>
       <c r="C20" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="22">
         <v>19</v>
       </c>
@@ -4539,10 +8753,10 @@
       </c>
       <c r="C21" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="22">
         <v>20</v>
       </c>
@@ -4551,7 +8765,7 @@
       </c>
       <c r="C22" s="22">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
